--- a/Test/OrthoMill1.xlsx
+++ b/Test/OrthoMill1.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTWhitney\PycharmProjects\ScheduleDateRefresher\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F277533C-B765-484A-8D91-FCA8945CDA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A89BAA9-20C5-448C-B35D-A98A9F55847C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31260" yWindow="675" windowWidth="21600" windowHeight="11385" tabRatio="206" xr2:uid="{7D91035E-7C02-4707-AA65-6CEC655CC548}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="206" xr2:uid="{7D91035E-7C02-4707-AA65-6CEC655CC548}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Schedule" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateCount="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Test/OrthoMill1.xlsx
+++ b/Test/OrthoMill1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTWhitney\PycharmProjects\ScheduleDateRefresher\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A4B021-5F27-43E6-9B4C-8346C4CAD45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23A4503-6954-4F68-A75C-CD225F653963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="206" xr2:uid="{7D91035E-7C02-4707-AA65-6CEC655CC548}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4002" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3894" uniqueCount="469">
   <si>
     <t xml:space="preserve"> MILLING 1 SCHEDULE</t>
   </si>
@@ -1326,9 +1326,6 @@
     <t>1.31</t>
   </si>
   <si>
-    <t>ROBO-14</t>
-  </si>
-  <si>
     <t>ASSET# 2247</t>
   </si>
   <si>
@@ -1349,102 +1346,6 @@
   </si>
   <si>
     <t>1.4</t>
-  </si>
-  <si>
-    <t>22-000RH-00</t>
-  </si>
-  <si>
-    <t>REAR HOOK</t>
-  </si>
-  <si>
-    <t>1" X 24" X 48" DELRIN 150 BLAC</t>
-  </si>
-  <si>
-    <t>P010174</t>
-  </si>
-  <si>
-    <t>22-000FH-00</t>
-  </si>
-  <si>
-    <t>FRONT HOOK</t>
-  </si>
-  <si>
-    <t>22-000CH-00</t>
-  </si>
-  <si>
-    <t>CENTER HOOK</t>
-  </si>
-  <si>
-    <t>C18414-01</t>
-  </si>
-  <si>
-    <t>N50399700-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLIDER BODY THUMB PAD  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ø1.000" 316L SST      </t>
-  </si>
-  <si>
-    <t>P0097824</t>
-  </si>
-  <si>
-    <t>AR-8737-38</t>
-  </si>
-  <si>
-    <t>50454100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T10 HEXALOBE, CMP FT     </t>
-  </si>
-  <si>
-    <t>C28971-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOP, REUSABLE DEPTH STOP  </t>
-  </si>
-  <si>
-    <t>PART # CHANGE COMING</t>
-  </si>
-  <si>
-    <t>P0097446</t>
-  </si>
-  <si>
-    <t>C28971-03</t>
-  </si>
-  <si>
-    <t>C28971-04</t>
-  </si>
-  <si>
-    <t>C28971-01</t>
-  </si>
-  <si>
-    <t>110040201-00</t>
-  </si>
-  <si>
-    <t>50452300</t>
-  </si>
-  <si>
-    <t>0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPR AUG MINI SI 2.7 DRL GD  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.125 ± .0005 17-4 RND H925   </t>
-  </si>
-  <si>
-    <t>P001579M</t>
-  </si>
-  <si>
-    <t>110040200-00</t>
-  </si>
-  <si>
-    <t>50461900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPR AUG MINI AP 2.7 DRL GD  </t>
   </si>
   <si>
     <t>ROBO-15</t>
@@ -1522,11 +1423,38 @@
   <si>
     <t>42517450710 HELLO</t>
   </si>
+  <si>
+    <t>fred</t>
+  </si>
+  <si>
+    <t>110029098-00</t>
+  </si>
+  <si>
+    <t>110029099-00</t>
+  </si>
+  <si>
+    <t>110029095-01</t>
+  </si>
+  <si>
+    <t>110029095-02</t>
+  </si>
+  <si>
+    <t>110029095-03</t>
+  </si>
+  <si>
+    <t>123456798-009</t>
+  </si>
+  <si>
+    <t>123456798-099</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1556,9 +1484,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1896,7 +1825,9 @@
   <dimension ref="A1:AF3252"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="32" width="27.85546875" customWidth="1"/>
+    <col min="1" max="3" width="27.85546875" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="32" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
@@ -2127,7 +2058,8 @@
         <v>45890</v>
       </c>
       <c r="AA8" s="1">
-        <v>45894</v>
+        <f t="shared" ref="AA8:AA13" ca="1" si="0">TODAY()</f>
+        <v>45896</v>
       </c>
       <c r="AB8">
         <v>3.9</v>
@@ -2150,7 +2082,7 @@
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>493</v>
+        <v>460</v>
       </c>
       <c r="E9">
         <v>50417700</v>
@@ -2210,6 +2142,7 @@
         <v>45897</v>
       </c>
       <c r="AA9" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>45896</v>
       </c>
       <c r="AB9">
@@ -2232,7 +2165,7 @@
       <c r="C10" t="s">
         <v>44</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>42527450810</v>
       </c>
       <c r="E10">
@@ -2290,7 +2223,8 @@
         <v>45908</v>
       </c>
       <c r="AA10" s="1">
-        <v>45904</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45896</v>
       </c>
       <c r="AB10">
         <v>3.8</v>
@@ -2370,7 +2304,8 @@
         <v>45910</v>
       </c>
       <c r="AA11" s="1">
-        <v>45908</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45896</v>
       </c>
       <c r="AB11">
         <v>3.9</v>
@@ -2450,7 +2385,8 @@
         <v>45911</v>
       </c>
       <c r="AA12" s="1">
-        <v>45910</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45896</v>
       </c>
       <c r="AB12">
         <v>4.8</v>
@@ -2530,7 +2466,8 @@
         <v>45916</v>
       </c>
       <c r="AA13" s="1">
-        <v>45911</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45896</v>
       </c>
       <c r="AB13">
         <v>4.4000000000000004</v>
@@ -7214,7 +7151,8 @@
     </row>
     <row r="153" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AA153" s="1">
-        <v>46008</v>
+        <f ca="1">TODAY()</f>
+        <v>45896</v>
       </c>
       <c r="AB153">
         <v>0</v>
@@ -9743,8 +9681,8 @@
       <c r="Z265">
         <v>45890</v>
       </c>
-      <c r="AA265" s="1">
-        <v>45894</v>
+      <c r="AA265" s="1" t="s">
+        <v>461</v>
       </c>
       <c r="AB265">
         <v>8.1999999999999993</v>
@@ -51361,14 +51299,11 @@
       </c>
     </row>
     <row r="1909" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1909" t="s">
-        <v>429</v>
-      </c>
       <c r="E1909" t="s">
         <v>5</v>
       </c>
       <c r="F1909" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I1909" t="s">
         <v>7</v>
@@ -51435,7 +51370,7 @@
         <v>21</v>
       </c>
       <c r="K1911" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L1911" t="s">
         <v>23</v>
@@ -51459,7 +51394,7 @@
         <v>29</v>
       </c>
       <c r="S1911" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T1911" t="s">
         <v>31</v>
@@ -51506,10 +51441,10 @@
         <v>44</v>
       </c>
       <c r="D1913" t="s">
+        <v>432</v>
+      </c>
+      <c r="E1913" t="s">
         <v>433</v>
-      </c>
-      <c r="E1913" t="s">
-        <v>434</v>
       </c>
       <c r="F1913" t="s">
         <v>45</v>
@@ -51524,7 +51459,7 @@
         <v>45957</v>
       </c>
       <c r="J1913" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K1913" t="s">
         <v>404</v>
@@ -51536,7 +51471,7 @@
         <v>49</v>
       </c>
       <c r="O1913" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P1913" t="s">
         <v>51</v>
@@ -51566,7 +51501,8 @@
         <v>45916</v>
       </c>
       <c r="AA1913" s="1">
-        <v>45916</v>
+        <f ca="1">TODAY()</f>
+        <v>45896</v>
       </c>
       <c r="AB1913">
         <v>9.9999999999999867E-2</v>
@@ -51584,7 +51520,10 @@
         <v>12.637362637362639</v>
       </c>
     </row>
-    <row r="1914" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1914" spans="1:32" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1914" t="s">
+        <v>464</v>
+      </c>
       <c r="AA1914" s="1">
         <v>45916</v>
       </c>
@@ -51605,1076 +51544,433 @@
       </c>
     </row>
     <row r="1915" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AA1915" s="1">
-        <v>45916</v>
-      </c>
-      <c r="AB1915">
-        <v>0</v>
-      </c>
-      <c r="AC1915">
-        <v>0</v>
-      </c>
-      <c r="AD1915">
-        <v>0</v>
-      </c>
-      <c r="AE1915">
-        <v>0</v>
-      </c>
-      <c r="AF1915">
-        <v>12.637362637362639</v>
+      <c r="D1915" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="1916" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AA1916" s="1">
-        <v>45916</v>
-      </c>
-      <c r="AB1916">
-        <v>0</v>
-      </c>
-      <c r="AC1916">
-        <v>0</v>
-      </c>
-      <c r="AD1916">
-        <v>0</v>
-      </c>
-      <c r="AE1916">
-        <v>0</v>
-      </c>
-      <c r="AF1916">
-        <v>12.637362637362639</v>
-      </c>
-    </row>
-    <row r="1917" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1917" t="s">
-        <v>210</v>
-      </c>
-      <c r="C1917" t="s">
-        <v>211</v>
-      </c>
-      <c r="D1917" t="s">
-        <v>437</v>
-      </c>
-      <c r="E1917" t="s">
-        <v>213</v>
-      </c>
-      <c r="F1917" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1917">
-        <v>20</v>
-      </c>
-      <c r="H1917">
-        <v>10</v>
-      </c>
-      <c r="I1917">
-        <v>45932</v>
-      </c>
-      <c r="J1917" t="s">
-        <v>438</v>
-      </c>
-      <c r="K1917" t="s">
-        <v>439</v>
-      </c>
-      <c r="L1917" t="s">
-        <v>440</v>
-      </c>
-      <c r="N1917" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1917">
-        <v>8</v>
-      </c>
-      <c r="P1917">
-        <v>10</v>
-      </c>
-      <c r="S1917" t="s">
-        <v>218</v>
-      </c>
-      <c r="T1917" t="s">
-        <v>70</v>
-      </c>
-      <c r="U1917" t="s">
-        <v>70</v>
-      </c>
-      <c r="V1917" t="s">
-        <v>70</v>
-      </c>
-      <c r="W1917" t="s">
-        <v>65</v>
-      </c>
-      <c r="X1917" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y1917">
-        <v>45926</v>
-      </c>
-      <c r="AA1917" s="1">
-        <v>45917</v>
-      </c>
-      <c r="AB1917">
-        <v>8</v>
-      </c>
-      <c r="AC1917">
-        <v>10</v>
-      </c>
-      <c r="AD1917">
-        <v>11.25</v>
-      </c>
-      <c r="AE1917">
-        <v>0.86538461538461542</v>
-      </c>
-      <c r="AF1917">
-        <v>13.502747252747254</v>
+      <c r="D1916" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="1918" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1918" t="s">
-        <v>210</v>
+        <v>12</v>
+      </c>
+      <c r="B1918" t="s">
+        <v>13</v>
       </c>
       <c r="C1918" t="s">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="D1918" t="s">
-        <v>441</v>
+        <v>15</v>
       </c>
       <c r="E1918" t="s">
-        <v>213</v>
+        <v>16</v>
       </c>
       <c r="F1918" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1918" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1918" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1918" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1918" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1918" t="s">
+        <v>430</v>
+      </c>
+      <c r="L1918" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1918" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1918" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1918" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1918" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1918" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1918" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1918" t="s">
+        <v>431</v>
+      </c>
+      <c r="T1918" t="s">
+        <v>31</v>
+      </c>
+      <c r="U1918" t="s">
+        <v>32</v>
+      </c>
+      <c r="V1918" t="s">
+        <v>33</v>
+      </c>
+      <c r="W1918" t="s">
+        <v>34</v>
+      </c>
+      <c r="X1918" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y1918" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z1918" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1918" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB1918" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC1918" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD1918" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1918" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF1918" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="C1920" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1920" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1920" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1920" t="s">
         <v>45</v>
       </c>
-      <c r="G1918">
+      <c r="G1920">
         <v>20</v>
       </c>
-      <c r="H1918">
-        <v>10</v>
-      </c>
-      <c r="I1918">
-        <v>45932</v>
-      </c>
-      <c r="J1918" t="s">
-        <v>442</v>
-      </c>
-      <c r="K1918" t="s">
-        <v>439</v>
-      </c>
-      <c r="L1918" t="s">
-        <v>440</v>
-      </c>
-      <c r="N1918" t="s">
+      <c r="H1920">
+        <v>240</v>
+      </c>
+      <c r="I1920">
+        <v>45957</v>
+      </c>
+      <c r="J1920" t="s">
+        <v>434</v>
+      </c>
+      <c r="K1920" t="s">
+        <v>404</v>
+      </c>
+      <c r="L1920" t="s">
+        <v>405</v>
+      </c>
+      <c r="N1920" t="s">
         <v>49</v>
       </c>
-      <c r="O1918" t="s">
-        <v>261</v>
-      </c>
-      <c r="P1918" t="s">
+      <c r="O1920" t="s">
+        <v>435</v>
+      </c>
+      <c r="P1920" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1920" t="s">
         <v>243</v>
       </c>
-      <c r="S1918" t="s">
-        <v>218</v>
-      </c>
-      <c r="T1918" t="s">
-        <v>70</v>
-      </c>
-      <c r="U1918" t="s">
-        <v>70</v>
-      </c>
-      <c r="V1918" t="s">
-        <v>70</v>
-      </c>
-      <c r="W1918" t="s">
-        <v>65</v>
-      </c>
-      <c r="X1918" t="s">
+      <c r="R1920" t="s">
+        <v>406</v>
+      </c>
+      <c r="T1920" t="s">
+        <v>53</v>
+      </c>
+      <c r="U1920" t="s">
+        <v>53</v>
+      </c>
+      <c r="V1920" t="s">
+        <v>53</v>
+      </c>
+      <c r="W1920" t="s">
+        <v>54</v>
+      </c>
+      <c r="X1920" t="s">
         <v>55</v>
       </c>
-      <c r="Y1918">
-        <v>45926</v>
-      </c>
-      <c r="AA1918" s="1">
-        <v>45918</v>
-      </c>
-      <c r="AB1918">
+      <c r="Y1920">
+        <v>45916</v>
+      </c>
+      <c r="AA1920" s="1">
+        <f ca="1">TODAY()</f>
+        <v>45896</v>
+      </c>
+      <c r="AB1920">
+        <v>9.9999999999999867E-2</v>
+      </c>
+      <c r="AC1920">
+        <v>230</v>
+      </c>
+      <c r="AD1920">
+        <v>164.28571428571431</v>
+      </c>
+      <c r="AE1920">
+        <v>12.637362637362639</v>
+      </c>
+      <c r="AF1920">
+        <v>12.637362637362639</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AA1925" s="1"/>
+    </row>
+    <row r="1926" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AA1926" s="1"/>
+    </row>
+    <row r="1927" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="E1927" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1927" t="s">
+        <v>429</v>
+      </c>
+      <c r="I1927" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1927">
+        <v>9</v>
+      </c>
+      <c r="K1927" t="s">
         <v>8</v>
       </c>
-      <c r="AC1918">
-        <v>10</v>
-      </c>
-      <c r="AD1918">
-        <v>11.25</v>
-      </c>
-      <c r="AE1918">
-        <v>0.86538461538461542</v>
-      </c>
-      <c r="AF1918">
-        <v>14.368131868131869</v>
-      </c>
-    </row>
-    <row r="1919" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1919" t="s">
-        <v>210</v>
-      </c>
-      <c r="C1919" t="s">
-        <v>211</v>
-      </c>
-      <c r="D1919" t="s">
-        <v>443</v>
-      </c>
-      <c r="E1919" t="s">
-        <v>213</v>
-      </c>
-      <c r="F1919" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1919">
-        <v>20</v>
-      </c>
-      <c r="H1919">
-        <v>10</v>
-      </c>
-      <c r="I1919">
-        <v>45932</v>
-      </c>
-      <c r="J1919" t="s">
-        <v>444</v>
-      </c>
-      <c r="K1919" t="s">
-        <v>439</v>
-      </c>
-      <c r="L1919" t="s">
-        <v>440</v>
-      </c>
-      <c r="N1919" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1919" t="s">
-        <v>243</v>
-      </c>
-      <c r="P1919" t="s">
-        <v>243</v>
-      </c>
-      <c r="S1919" t="s">
-        <v>218</v>
-      </c>
-      <c r="T1919" t="s">
-        <v>70</v>
-      </c>
-      <c r="U1919" t="s">
-        <v>70</v>
-      </c>
-      <c r="V1919" t="s">
-        <v>70</v>
-      </c>
-      <c r="W1919" t="s">
-        <v>65</v>
-      </c>
-      <c r="X1919" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y1919">
-        <v>45926</v>
-      </c>
-      <c r="AA1919" s="1">
-        <v>45922</v>
-      </c>
-      <c r="AB1919">
-        <v>10</v>
-      </c>
-      <c r="AC1919">
-        <v>10</v>
-      </c>
-      <c r="AD1919">
+      <c r="L1927" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="C1928" t="s">
+        <v>400</v>
+      </c>
+      <c r="E1928">
+        <v>13</v>
+      </c>
+      <c r="F1928" t="s">
+        <v>385</v>
+      </c>
+      <c r="I1928" t="s">
         <v>11</v>
       </c>
-      <c r="AE1919">
-        <v>0.84615384615384615</v>
-      </c>
-      <c r="AF1919">
-        <v>15.214285714285715</v>
-      </c>
-    </row>
-    <row r="1920" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AA1920" s="1">
-        <v>45922</v>
-      </c>
-      <c r="AB1920">
-        <v>0</v>
-      </c>
-      <c r="AC1920">
-        <v>0</v>
-      </c>
-      <c r="AD1920">
-        <v>0</v>
-      </c>
-      <c r="AE1920">
-        <v>0</v>
-      </c>
-      <c r="AF1920">
-        <v>15.214285714285715</v>
-      </c>
-    </row>
-    <row r="1921" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AA1921" s="1">
-        <v>45922</v>
-      </c>
-      <c r="AB1921">
-        <v>0</v>
-      </c>
-      <c r="AC1921">
-        <v>0</v>
-      </c>
-      <c r="AD1921">
-        <v>0</v>
-      </c>
-      <c r="AE1921">
-        <v>0</v>
-      </c>
-      <c r="AF1921">
-        <v>15.214285714285715</v>
-      </c>
-    </row>
-    <row r="1922" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="C1922" t="s">
-        <v>196</v>
-      </c>
-      <c r="D1922" t="s">
-        <v>445</v>
-      </c>
-      <c r="E1922" t="s">
-        <v>446</v>
-      </c>
-      <c r="G1922">
-        <v>20</v>
-      </c>
-      <c r="H1922">
-        <v>64</v>
-      </c>
-      <c r="I1922">
-        <v>45985</v>
-      </c>
-      <c r="J1922" t="s">
-        <v>447</v>
-      </c>
-      <c r="K1922" t="s">
-        <v>448</v>
-      </c>
-      <c r="L1922" t="s">
-        <v>449</v>
-      </c>
-      <c r="N1922" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1922" t="s">
-        <v>131</v>
-      </c>
-      <c r="P1922" t="s">
-        <v>131</v>
-      </c>
-      <c r="T1922" t="s">
-        <v>53</v>
-      </c>
-      <c r="U1922" t="s">
-        <v>70</v>
-      </c>
-      <c r="V1922" t="s">
-        <v>70</v>
-      </c>
-      <c r="W1922" t="s">
-        <v>421</v>
-      </c>
-      <c r="X1922" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y1922">
-        <v>45924</v>
-      </c>
-      <c r="AA1922" s="1">
-        <v>45923</v>
-      </c>
-      <c r="AB1922">
-        <v>6</v>
-      </c>
-      <c r="AC1922">
-        <v>64</v>
-      </c>
-      <c r="AD1922">
-        <v>16.666666666666664</v>
-      </c>
-      <c r="AE1922">
-        <v>1.2820512820512819</v>
-      </c>
-      <c r="AF1922">
-        <v>16.496336996336996</v>
-      </c>
-    </row>
-    <row r="1923" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AA1923" s="1">
-        <v>45923</v>
-      </c>
-      <c r="AB1923">
-        <v>0</v>
-      </c>
-      <c r="AC1923">
-        <v>0</v>
-      </c>
-      <c r="AD1923">
-        <v>0</v>
-      </c>
-      <c r="AE1923">
-        <v>0</v>
-      </c>
-      <c r="AF1923">
-        <v>16.496336996336996</v>
-      </c>
-    </row>
-    <row r="1924" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="C1924" t="s">
-        <v>196</v>
-      </c>
-      <c r="D1924" t="s">
-        <v>450</v>
-      </c>
-      <c r="E1924" t="s">
-        <v>451</v>
-      </c>
-      <c r="F1924" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1924">
-        <v>17</v>
-      </c>
-      <c r="H1924">
-        <v>500</v>
-      </c>
-      <c r="I1924">
-        <v>46000</v>
-      </c>
-      <c r="J1924" t="s">
-        <v>452</v>
-      </c>
-      <c r="N1924" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1924" t="s">
-        <v>243</v>
-      </c>
-      <c r="P1924" t="s">
-        <v>62</v>
-      </c>
-      <c r="T1924" t="s">
-        <v>53</v>
-      </c>
-      <c r="U1924" t="s">
-        <v>70</v>
-      </c>
-      <c r="V1924" t="s">
-        <v>70</v>
-      </c>
-      <c r="W1924" t="s">
-        <v>65</v>
-      </c>
-      <c r="X1924" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y1924">
-        <v>45951</v>
-      </c>
-      <c r="AA1924" s="1">
-        <v>45930</v>
-      </c>
-      <c r="AB1924">
-        <v>10</v>
-      </c>
-      <c r="AC1924">
-        <v>500</v>
-      </c>
-      <c r="AD1924">
-        <v>54</v>
-      </c>
-      <c r="AE1924">
-        <v>4.1538461538461542</v>
-      </c>
-      <c r="AF1924">
-        <v>20.65018315018315</v>
-      </c>
-    </row>
-    <row r="1925" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="C1925" t="s">
-        <v>196</v>
-      </c>
-      <c r="D1925" t="s">
-        <v>450</v>
-      </c>
-      <c r="E1925" t="s">
-        <v>451</v>
-      </c>
-      <c r="F1925" t="s">
-        <v>227</v>
-      </c>
-      <c r="G1925">
-        <v>17</v>
-      </c>
-      <c r="H1925">
-        <v>500</v>
-      </c>
-      <c r="I1925">
-        <v>46021</v>
-      </c>
-      <c r="J1925" t="s">
-        <v>452</v>
-      </c>
-      <c r="N1925" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1925" t="s">
-        <v>243</v>
-      </c>
-      <c r="P1925" t="s">
-        <v>62</v>
-      </c>
-      <c r="T1925" t="s">
-        <v>53</v>
-      </c>
-      <c r="U1925" t="s">
-        <v>70</v>
-      </c>
-      <c r="V1925" t="s">
-        <v>70</v>
-      </c>
-      <c r="W1925" t="s">
-        <v>65</v>
-      </c>
-      <c r="X1925" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y1925">
-        <v>45974</v>
-      </c>
-      <c r="AA1925" s="1">
-        <v>45937</v>
-      </c>
-      <c r="AB1925">
-        <v>10</v>
-      </c>
-      <c r="AC1925">
-        <v>500</v>
-      </c>
-      <c r="AD1925">
-        <v>54</v>
-      </c>
-      <c r="AE1925">
-        <v>4.1538461538461542</v>
-      </c>
-      <c r="AF1925">
-        <v>24.804029304029303</v>
-      </c>
-    </row>
-    <row r="1926" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AA1926" s="1">
-        <v>45937</v>
-      </c>
-      <c r="AB1926">
-        <v>0</v>
-      </c>
-      <c r="AC1926">
-        <v>0</v>
-      </c>
-      <c r="AD1926">
-        <v>0</v>
-      </c>
-      <c r="AE1926">
-        <v>0</v>
-      </c>
-      <c r="AF1926">
-        <v>24.804029304029303</v>
-      </c>
-    </row>
-    <row r="1927" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1927" t="s">
-        <v>210</v>
-      </c>
-      <c r="C1927" t="s">
-        <v>196</v>
-      </c>
-      <c r="D1927" t="s">
-        <v>453</v>
-      </c>
-      <c r="G1927">
-        <v>30</v>
-      </c>
-      <c r="H1927">
-        <v>230</v>
-      </c>
-      <c r="I1927">
-        <v>45805</v>
-      </c>
-      <c r="J1927" t="s">
-        <v>454</v>
-      </c>
-      <c r="K1927" t="s">
-        <v>455</v>
-      </c>
-      <c r="L1927" t="s">
-        <v>456</v>
-      </c>
-      <c r="N1927" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1927" t="s">
-        <v>242</v>
-      </c>
-      <c r="P1927" t="s">
-        <v>243</v>
-      </c>
-      <c r="S1927" t="s">
-        <v>284</v>
-      </c>
-      <c r="T1927" t="s">
-        <v>70</v>
-      </c>
-      <c r="U1927" t="s">
-        <v>53</v>
-      </c>
-      <c r="V1927" t="s">
-        <v>53</v>
-      </c>
-      <c r="W1927" t="s">
-        <v>421</v>
-      </c>
-      <c r="X1927" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA1927" s="1">
-        <v>45945</v>
-      </c>
-      <c r="AB1927">
-        <v>5</v>
-      </c>
-      <c r="AC1927">
-        <v>230</v>
-      </c>
-      <c r="AD1927">
-        <v>56</v>
-      </c>
-      <c r="AE1927">
-        <v>4.3076923076923075</v>
-      </c>
-      <c r="AF1927">
-        <v>29.11172161172161</v>
-      </c>
-    </row>
-    <row r="1928" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1928" t="s">
-        <v>210</v>
-      </c>
-      <c r="C1928" t="s">
-        <v>196</v>
-      </c>
-      <c r="D1928" t="s">
-        <v>457</v>
-      </c>
-      <c r="G1928">
-        <v>30</v>
-      </c>
-      <c r="H1928">
-        <v>205</v>
-      </c>
-      <c r="I1928">
-        <v>45797</v>
-      </c>
-      <c r="J1928" t="s">
-        <v>454</v>
-      </c>
-      <c r="K1928" t="s">
-        <v>455</v>
-      </c>
-      <c r="L1928" t="s">
-        <v>456</v>
-      </c>
-      <c r="N1928" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1928" t="s">
-        <v>242</v>
-      </c>
-      <c r="P1928" t="s">
-        <v>62</v>
-      </c>
-      <c r="S1928" t="s">
-        <v>284</v>
-      </c>
-      <c r="T1928" t="s">
-        <v>70</v>
-      </c>
-      <c r="U1928" t="s">
-        <v>53</v>
-      </c>
-      <c r="V1928" t="s">
-        <v>53</v>
-      </c>
-      <c r="W1928" t="s">
-        <v>421</v>
-      </c>
-      <c r="X1928" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA1928" s="1">
-        <v>45951</v>
-      </c>
-      <c r="AB1928">
-        <v>5</v>
-      </c>
-      <c r="AC1928">
-        <v>205</v>
-      </c>
-      <c r="AD1928">
-        <v>45</v>
-      </c>
-      <c r="AE1928">
-        <v>3.4615384615384617</v>
-      </c>
-      <c r="AF1928">
-        <v>32.573260073260073</v>
+      <c r="J1928">
+        <v>2</v>
+      </c>
+      <c r="K1928">
+        <v>0.77777777777777779</v>
       </c>
     </row>
     <row r="1929" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1929" t="s">
-        <v>210</v>
+        <v>12</v>
+      </c>
+      <c r="B1929" t="s">
+        <v>13</v>
       </c>
       <c r="C1929" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="D1929" t="s">
-        <v>458</v>
-      </c>
-      <c r="G1929">
-        <v>30</v>
-      </c>
-      <c r="H1929">
-        <v>205</v>
-      </c>
-      <c r="I1929">
-        <v>45799</v>
+        <v>15</v>
+      </c>
+      <c r="E1929" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1929" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1929" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1929" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1929" t="s">
+        <v>20</v>
       </c>
       <c r="J1929" t="s">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="K1929" t="s">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="L1929" t="s">
-        <v>456</v>
+        <v>23</v>
+      </c>
+      <c r="M1929" t="s">
+        <v>24</v>
       </c>
       <c r="N1929" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1929" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1929" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1929" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1929" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1929" t="s">
+        <v>431</v>
+      </c>
+      <c r="T1929" t="s">
+        <v>31</v>
+      </c>
+      <c r="U1929" t="s">
+        <v>32</v>
+      </c>
+      <c r="V1929" t="s">
+        <v>33</v>
+      </c>
+      <c r="W1929" t="s">
+        <v>34</v>
+      </c>
+      <c r="X1929" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y1929" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z1929" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1929" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB1929" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC1929" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD1929" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1929" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF1929" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="C1931" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1931" t="s">
+        <v>463</v>
+      </c>
+      <c r="E1931" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1931" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1931">
+        <v>20</v>
+      </c>
+      <c r="H1931">
+        <v>240</v>
+      </c>
+      <c r="I1931">
+        <v>45957</v>
+      </c>
+      <c r="J1931" t="s">
+        <v>434</v>
+      </c>
+      <c r="K1931" t="s">
+        <v>404</v>
+      </c>
+      <c r="L1931" t="s">
+        <v>405</v>
+      </c>
+      <c r="N1931" t="s">
         <v>49</v>
       </c>
-      <c r="O1929" t="s">
-        <v>242</v>
-      </c>
-      <c r="P1929" t="s">
-        <v>62</v>
-      </c>
-      <c r="S1929" t="s">
-        <v>284</v>
-      </c>
-      <c r="T1929" t="s">
-        <v>70</v>
-      </c>
-      <c r="U1929" t="s">
+      <c r="O1931" t="s">
+        <v>435</v>
+      </c>
+      <c r="P1931" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1931" t="s">
+        <v>243</v>
+      </c>
+      <c r="R1931" t="s">
+        <v>406</v>
+      </c>
+      <c r="T1931" t="s">
         <v>53</v>
       </c>
-      <c r="V1929" t="s">
+      <c r="U1931" t="s">
         <v>53</v>
       </c>
-      <c r="W1929" t="s">
-        <v>421</v>
-      </c>
-      <c r="X1929" t="s">
+      <c r="V1931" t="s">
+        <v>53</v>
+      </c>
+      <c r="W1931" t="s">
+        <v>54</v>
+      </c>
+      <c r="X1931" t="s">
         <v>55</v>
       </c>
-      <c r="AA1929" s="1">
-        <v>45958</v>
-      </c>
-      <c r="AB1929">
-        <v>5</v>
-      </c>
-      <c r="AC1929">
-        <v>205</v>
-      </c>
-      <c r="AD1929">
-        <v>45</v>
-      </c>
-      <c r="AE1929">
-        <v>3.4615384615384617</v>
-      </c>
-      <c r="AF1929">
-        <v>36.034798534798533</v>
-      </c>
-    </row>
-    <row r="1930" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1930" t="s">
-        <v>210</v>
-      </c>
-      <c r="C1930" t="s">
-        <v>196</v>
-      </c>
-      <c r="D1930" t="s">
-        <v>459</v>
-      </c>
-      <c r="G1930">
-        <v>30</v>
-      </c>
-      <c r="H1930">
-        <v>25</v>
-      </c>
-      <c r="I1930">
-        <v>45805</v>
-      </c>
-      <c r="J1930" t="s">
-        <v>454</v>
-      </c>
-      <c r="K1930" t="s">
-        <v>455</v>
-      </c>
-      <c r="L1930" t="s">
-        <v>456</v>
-      </c>
-      <c r="N1930" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1930" t="s">
-        <v>242</v>
-      </c>
-      <c r="P1930" t="s">
-        <v>62</v>
-      </c>
-      <c r="S1930" t="s">
-        <v>284</v>
-      </c>
-      <c r="T1930" t="s">
-        <v>70</v>
-      </c>
-      <c r="U1930" t="s">
-        <v>53</v>
-      </c>
-      <c r="V1930" t="s">
-        <v>53</v>
-      </c>
-      <c r="W1930" t="s">
-        <v>421</v>
-      </c>
-      <c r="X1930" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA1930" s="1">
-        <v>45958</v>
-      </c>
-      <c r="AB1930">
-        <v>5</v>
-      </c>
-      <c r="AC1930">
-        <v>25</v>
-      </c>
-      <c r="AD1930">
-        <v>9</v>
-      </c>
-      <c r="AE1930">
-        <v>0.69230769230769229</v>
-      </c>
-      <c r="AF1930">
-        <v>36.727106227106226</v>
-      </c>
-    </row>
-    <row r="1931" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="Y1931">
+        <v>45916</v>
+      </c>
       <c r="AA1931" s="1">
-        <v>45958</v>
+        <f ca="1">TODAY()</f>
+        <v>45896</v>
       </c>
       <c r="AB1931">
-        <v>0</v>
+        <v>9.9999999999999867E-2</v>
       </c>
       <c r="AC1931">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AD1931">
-        <v>0</v>
+        <v>164.28571428571431</v>
       </c>
       <c r="AE1931">
-        <v>0</v>
+        <v>12.637362637362639</v>
       </c>
       <c r="AF1931">
-        <v>36.727106227106226</v>
+        <v>12.637362637362639</v>
       </c>
     </row>
     <row r="1932" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AA1932" s="1">
-        <v>45958</v>
-      </c>
-      <c r="AB1932">
-        <v>0</v>
-      </c>
-      <c r="AC1932">
-        <v>0</v>
-      </c>
-      <c r="AD1932">
-        <v>0</v>
-      </c>
-      <c r="AE1932">
-        <v>0</v>
-      </c>
-      <c r="AF1932">
-        <v>36.727106227106226</v>
-      </c>
+      <c r="AA1932" s="1"/>
     </row>
     <row r="1933" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="C1933" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1933" t="s">
-        <v>460</v>
-      </c>
-      <c r="E1933" t="s">
-        <v>461</v>
-      </c>
-      <c r="F1933" t="s">
-        <v>462</v>
-      </c>
-      <c r="G1933">
-        <v>20</v>
-      </c>
-      <c r="H1933">
-        <v>240</v>
-      </c>
-      <c r="J1933" t="s">
-        <v>463</v>
-      </c>
-      <c r="K1933" t="s">
-        <v>464</v>
-      </c>
-      <c r="L1933" t="s">
-        <v>465</v>
-      </c>
-      <c r="N1933" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1933" t="s">
-        <v>406</v>
-      </c>
-      <c r="P1933" t="s">
-        <v>329</v>
-      </c>
-      <c r="T1933" t="s">
-        <v>53</v>
-      </c>
-      <c r="U1933" t="s">
-        <v>70</v>
-      </c>
-      <c r="V1933" t="s">
-        <v>70</v>
-      </c>
-      <c r="W1933" t="s">
-        <v>65</v>
-      </c>
-      <c r="X1933" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y1933">
-        <v>45980</v>
-      </c>
-      <c r="AA1933" s="1">
-        <v>45985</v>
-      </c>
-      <c r="AB1933">
-        <v>1.3</v>
-      </c>
-      <c r="AC1933">
-        <v>240</v>
-      </c>
-      <c r="AD1933">
-        <v>187.61538461538461</v>
-      </c>
-      <c r="AE1933">
-        <v>14.431952662721894</v>
-      </c>
-      <c r="AF1933">
-        <v>51.159058889828117</v>
-      </c>
+      <c r="AA1933" s="1"/>
     </row>
     <row r="1934" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="C1934" t="s">
-        <v>422</v>
-      </c>
-      <c r="D1934" t="s">
-        <v>466</v>
-      </c>
-      <c r="E1934" t="s">
-        <v>467</v>
-      </c>
-      <c r="F1934" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1934">
-        <v>20</v>
-      </c>
-      <c r="H1934">
-        <v>240</v>
-      </c>
-      <c r="I1934">
-        <v>46044</v>
-      </c>
-      <c r="J1934" t="s">
-        <v>468</v>
-      </c>
-      <c r="K1934" t="s">
-        <v>404</v>
-      </c>
-      <c r="L1934" t="s">
-        <v>405</v>
-      </c>
-      <c r="N1934" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1934" t="s">
-        <v>406</v>
-      </c>
-      <c r="P1934" t="s">
-        <v>329</v>
-      </c>
-      <c r="T1934" t="s">
-        <v>53</v>
-      </c>
-      <c r="U1934" t="s">
-        <v>70</v>
-      </c>
-      <c r="V1934" t="s">
-        <v>70</v>
-      </c>
-      <c r="W1934" t="s">
-        <v>65</v>
-      </c>
-      <c r="X1934" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y1934">
-        <v>46014</v>
-      </c>
-      <c r="AA1934" s="1">
-        <v>46020</v>
-      </c>
-      <c r="AB1934">
-        <v>1.3</v>
-      </c>
-      <c r="AC1934">
-        <v>240</v>
-      </c>
-      <c r="AD1934">
-        <v>187.61538461538461</v>
-      </c>
-      <c r="AE1934">
-        <v>14.431952662721894</v>
-      </c>
-      <c r="AF1934">
-        <v>65.591011552550015</v>
-      </c>
+      <c r="AA1934" s="1"/>
     </row>
     <row r="1935" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AA1935" s="1">
@@ -54252,13 +53548,13 @@
     </row>
     <row r="2014" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2014" t="s">
-        <v>469</v>
+        <v>436</v>
       </c>
       <c r="E2014" t="s">
         <v>5</v>
       </c>
       <c r="F2014" t="s">
-        <v>470</v>
+        <v>437</v>
       </c>
       <c r="I2014" t="s">
         <v>7</v>
@@ -54270,7 +53566,7 @@
         <v>8</v>
       </c>
       <c r="L2014" t="s">
-        <v>471</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2015" spans="1:32" x14ac:dyDescent="0.25">
@@ -54393,7 +53689,7 @@
         <v>376</v>
       </c>
       <c r="D2018" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="E2018">
         <v>50462400</v>
@@ -54411,19 +53707,19 @@
         <v>45917</v>
       </c>
       <c r="J2018" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="K2018" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="L2018" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N2018" t="s">
         <v>49</v>
       </c>
       <c r="O2018" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="P2018" t="s">
         <v>51</v>
@@ -54473,7 +53769,7 @@
         <v>376</v>
       </c>
       <c r="D2019" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="E2019">
         <v>50462400</v>
@@ -54491,19 +53787,19 @@
         <v>45958</v>
       </c>
       <c r="J2019" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="K2019" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="L2019" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N2019" t="s">
         <v>49</v>
       </c>
       <c r="O2019" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="P2019" t="s">
         <v>49</v>
@@ -54553,7 +53849,7 @@
         <v>376</v>
       </c>
       <c r="D2020" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="E2020">
         <v>50462400</v>
@@ -54571,19 +53867,19 @@
         <v>45958</v>
       </c>
       <c r="J2020" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="K2020" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="L2020" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N2020" t="s">
         <v>49</v>
       </c>
       <c r="O2020" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="P2020" t="s">
         <v>49</v>
@@ -54633,7 +53929,7 @@
         <v>376</v>
       </c>
       <c r="D2021" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="E2021">
         <v>50462400</v>
@@ -54651,19 +53947,19 @@
         <v>45958</v>
       </c>
       <c r="J2021" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="K2021" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="L2021" t="s">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="N2021" t="s">
         <v>49</v>
       </c>
       <c r="O2021" t="s">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="P2021" t="s">
         <v>49</v>
@@ -56641,13 +55937,13 @@
     </row>
     <row r="2119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2119" t="s">
-        <v>477</v>
+        <v>444</v>
       </c>
       <c r="E2119" t="s">
         <v>5</v>
       </c>
       <c r="F2119" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="I2119" t="s">
         <v>7</v>
@@ -56661,13 +55957,13 @@
     </row>
     <row r="2120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2120" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="E2120">
         <v>9</v>
       </c>
       <c r="F2120" t="s">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="I2120" t="s">
         <v>11</v>
@@ -56711,7 +56007,7 @@
         <v>21</v>
       </c>
       <c r="K2121" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L2121" t="s">
         <v>23</v>
@@ -56735,7 +56031,7 @@
         <v>29</v>
       </c>
       <c r="S2121" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T2121" t="s">
         <v>31</v>
@@ -58813,13 +58109,13 @@
     </row>
     <row r="2225" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2225" t="s">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="E2225" t="s">
         <v>5</v>
       </c>
       <c r="F2225" t="s">
-        <v>482</v>
+        <v>449</v>
       </c>
       <c r="I2225" t="s">
         <v>7</v>
@@ -58833,7 +58129,7 @@
     </row>
     <row r="2226" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2226" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E2226">
         <v>1</v>
@@ -58951,10 +58247,10 @@
         <v>254</v>
       </c>
       <c r="D2229" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2229" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="AA2229" s="1">
         <v>45894</v>
@@ -58980,10 +58276,10 @@
         <v>254</v>
       </c>
       <c r="D2230" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2230" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2230" s="1">
         <v>45894</v>
@@ -59009,10 +58305,10 @@
         <v>254</v>
       </c>
       <c r="D2231" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2231" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2231" s="1">
         <v>45894</v>
@@ -59038,10 +58334,10 @@
         <v>254</v>
       </c>
       <c r="D2232" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2232" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2232" s="1">
         <v>45894</v>
@@ -59067,10 +58363,10 @@
         <v>254</v>
       </c>
       <c r="D2233" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2233" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2233" s="1">
         <v>45894</v>
@@ -59096,10 +58392,10 @@
         <v>254</v>
       </c>
       <c r="D2234" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2234" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2234" s="1">
         <v>45894</v>
@@ -59125,10 +58421,10 @@
         <v>254</v>
       </c>
       <c r="D2235" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2235" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2235" s="1">
         <v>45894</v>
@@ -59154,10 +58450,10 @@
         <v>254</v>
       </c>
       <c r="D2236" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2236" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2236" s="1">
         <v>45894</v>
@@ -59183,10 +58479,10 @@
         <v>254</v>
       </c>
       <c r="D2237" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2237" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2237" s="1">
         <v>45894</v>
@@ -59212,10 +58508,10 @@
         <v>254</v>
       </c>
       <c r="D2238" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2238" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2238" s="1">
         <v>45894</v>
@@ -59241,10 +58537,10 @@
         <v>254</v>
       </c>
       <c r="D2239" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2239" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2239" s="1">
         <v>45894</v>
@@ -59270,10 +58566,10 @@
         <v>254</v>
       </c>
       <c r="D2240" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2240" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2240" s="1">
         <v>45894</v>
@@ -59299,10 +58595,10 @@
         <v>254</v>
       </c>
       <c r="D2241" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2241" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2241" s="1">
         <v>45894</v>
@@ -59328,10 +58624,10 @@
         <v>254</v>
       </c>
       <c r="D2242" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2242" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2242" s="1">
         <v>45894</v>
@@ -59357,10 +58653,10 @@
         <v>254</v>
       </c>
       <c r="D2243" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2243" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2243" s="1">
         <v>45894</v>
@@ -59386,10 +58682,10 @@
         <v>254</v>
       </c>
       <c r="D2244" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2244" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2244" s="1">
         <v>45894</v>
@@ -59415,10 +58711,10 @@
         <v>254</v>
       </c>
       <c r="D2245" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2245" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2245" s="1">
         <v>45894</v>
@@ -59444,10 +58740,10 @@
         <v>254</v>
       </c>
       <c r="D2246" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2246" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2246" s="1">
         <v>45894</v>
@@ -59473,10 +58769,10 @@
         <v>254</v>
       </c>
       <c r="D2247" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2247" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2247" s="1">
         <v>45894</v>
@@ -59502,10 +58798,10 @@
         <v>254</v>
       </c>
       <c r="D2248" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2248" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2248" s="1">
         <v>45894</v>
@@ -59531,10 +58827,10 @@
         <v>254</v>
       </c>
       <c r="D2249" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2249" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2249" s="1">
         <v>45894</v>
@@ -59560,10 +58856,10 @@
         <v>254</v>
       </c>
       <c r="D2250" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2250" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2250" s="1">
         <v>45894</v>
@@ -59589,10 +58885,10 @@
         <v>254</v>
       </c>
       <c r="D2251" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2251" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2251" s="1">
         <v>45894</v>
@@ -59618,10 +58914,10 @@
         <v>254</v>
       </c>
       <c r="D2252" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2252" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2252" s="1">
         <v>45894</v>
@@ -59647,10 +58943,10 @@
         <v>254</v>
       </c>
       <c r="D2253" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2253" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2253" s="1">
         <v>45894</v>
@@ -59676,10 +58972,10 @@
         <v>254</v>
       </c>
       <c r="D2254" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2254" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2254" s="1">
         <v>45894</v>
@@ -59705,10 +59001,10 @@
         <v>254</v>
       </c>
       <c r="D2255" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2255" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2255" s="1">
         <v>45894</v>
@@ -59734,10 +59030,10 @@
         <v>254</v>
       </c>
       <c r="D2256" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2256" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2256" s="1">
         <v>45894</v>
@@ -59763,10 +59059,10 @@
         <v>254</v>
       </c>
       <c r="D2257" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2257" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2257" s="1">
         <v>45894</v>
@@ -59792,10 +59088,10 @@
         <v>254</v>
       </c>
       <c r="D2258" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2258" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2258" s="1">
         <v>45894</v>
@@ -59821,10 +59117,10 @@
         <v>254</v>
       </c>
       <c r="D2259" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2259" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2259" s="1">
         <v>45894</v>
@@ -59850,10 +59146,10 @@
         <v>254</v>
       </c>
       <c r="D2260" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2260" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2260" s="1">
         <v>45894</v>
@@ -59879,10 +59175,10 @@
         <v>254</v>
       </c>
       <c r="D2261" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2261" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2261" s="1">
         <v>45894</v>
@@ -59908,10 +59204,10 @@
         <v>254</v>
       </c>
       <c r="D2262" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2262" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2262" s="1">
         <v>45894</v>
@@ -59937,10 +59233,10 @@
         <v>254</v>
       </c>
       <c r="D2263" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2263" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2263" s="1">
         <v>45894</v>
@@ -59966,10 +59262,10 @@
         <v>254</v>
       </c>
       <c r="D2264" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2264" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2264" s="1">
         <v>45894</v>
@@ -59995,10 +59291,10 @@
         <v>254</v>
       </c>
       <c r="D2265" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2265" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2265" s="1">
         <v>45894</v>
@@ -60024,10 +59320,10 @@
         <v>254</v>
       </c>
       <c r="D2266" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2266" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2266" s="1">
         <v>45894</v>
@@ -60053,10 +59349,10 @@
         <v>254</v>
       </c>
       <c r="D2267" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2267" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2267" s="1">
         <v>45894</v>
@@ -60082,10 +59378,10 @@
         <v>254</v>
       </c>
       <c r="D2268" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2268" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2268" s="1">
         <v>45894</v>
@@ -60111,10 +59407,10 @@
         <v>254</v>
       </c>
       <c r="D2269" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2269" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2269" s="1">
         <v>45894</v>
@@ -60140,10 +59436,10 @@
         <v>254</v>
       </c>
       <c r="D2270" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="K2270" t="s">
-        <v>484</v>
+        <v>451</v>
       </c>
       <c r="AA2270" s="1">
         <v>45894</v>
@@ -61340,13 +60636,13 @@
     </row>
     <row r="2330" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2330" t="s">
-        <v>486</v>
+        <v>453</v>
       </c>
       <c r="E2330" t="s">
         <v>5</v>
       </c>
       <c r="F2330" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="I2330" t="s">
         <v>7</v>
@@ -61360,7 +60656,7 @@
     </row>
     <row r="2331" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2331" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="E2331">
         <v>1</v>
@@ -61477,11 +60773,11 @@
       <c r="A2334" t="s">
         <v>254</v>
       </c>
-      <c r="D2334" t="s">
-        <v>484</v>
+      <c r="D2334">
+        <v>123456789</v>
       </c>
       <c r="K2334" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="AA2334" s="1">
         <v>45894</v>
@@ -61503,383 +60799,45 @@
       </c>
     </row>
     <row r="2335" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2335" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2335" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2335" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2335" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2335">
-        <v>0</v>
-      </c>
-      <c r="AC2335">
-        <v>0</v>
-      </c>
-      <c r="AD2335">
-        <v>0</v>
-      </c>
-      <c r="AE2335">
-        <v>0</v>
-      </c>
-      <c r="AF2335">
-        <v>0</v>
-      </c>
+      <c r="AA2335" s="1"/>
     </row>
     <row r="2336" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2336" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2336" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2336" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2336" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2336">
-        <v>0</v>
-      </c>
-      <c r="AC2336">
-        <v>0</v>
-      </c>
-      <c r="AD2336">
-        <v>0</v>
-      </c>
-      <c r="AE2336">
-        <v>0</v>
-      </c>
-      <c r="AF2336">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2337" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2337" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2337" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2337" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2337" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2337">
-        <v>0</v>
-      </c>
-      <c r="AC2337">
-        <v>0</v>
-      </c>
-      <c r="AD2337">
-        <v>0</v>
-      </c>
-      <c r="AE2337">
-        <v>0</v>
-      </c>
-      <c r="AF2337">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2338" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2338" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2338" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2338" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2338" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2338">
-        <v>0</v>
-      </c>
-      <c r="AC2338">
-        <v>0</v>
-      </c>
-      <c r="AD2338">
-        <v>0</v>
-      </c>
-      <c r="AE2338">
-        <v>0</v>
-      </c>
-      <c r="AF2338">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2339" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2339" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2339" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2339" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2339" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2339">
-        <v>0</v>
-      </c>
-      <c r="AC2339">
-        <v>0</v>
-      </c>
-      <c r="AD2339">
-        <v>0</v>
-      </c>
-      <c r="AE2339">
-        <v>0</v>
-      </c>
-      <c r="AF2339">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2340" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2340" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2340" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2340" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2340" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2340">
-        <v>0</v>
-      </c>
-      <c r="AC2340">
-        <v>0</v>
-      </c>
-      <c r="AD2340">
-        <v>0</v>
-      </c>
-      <c r="AE2340">
-        <v>0</v>
-      </c>
-      <c r="AF2340">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2341" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2341" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2341" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2341" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2341" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2341">
-        <v>0</v>
-      </c>
-      <c r="AC2341">
-        <v>0</v>
-      </c>
-      <c r="AD2341">
-        <v>0</v>
-      </c>
-      <c r="AE2341">
-        <v>0</v>
-      </c>
-      <c r="AF2341">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2342" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2342" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2342" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2342" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2342" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2342">
-        <v>0</v>
-      </c>
-      <c r="AC2342">
-        <v>0</v>
-      </c>
-      <c r="AD2342">
-        <v>0</v>
-      </c>
-      <c r="AE2342">
-        <v>0</v>
-      </c>
-      <c r="AF2342">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2343" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2343" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2343" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2343" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2343" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2343">
-        <v>0</v>
-      </c>
-      <c r="AC2343">
-        <v>0</v>
-      </c>
-      <c r="AD2343">
-        <v>0</v>
-      </c>
-      <c r="AE2343">
-        <v>0</v>
-      </c>
-      <c r="AF2343">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2344" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2344" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2344" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2344" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2344" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2344">
-        <v>0</v>
-      </c>
-      <c r="AC2344">
-        <v>0</v>
-      </c>
-      <c r="AD2344">
-        <v>0</v>
-      </c>
-      <c r="AE2344">
-        <v>0</v>
-      </c>
-      <c r="AF2344">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2345" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2345" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2345" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2345" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2345" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2345">
-        <v>0</v>
-      </c>
-      <c r="AC2345">
-        <v>0</v>
-      </c>
-      <c r="AD2345">
-        <v>0</v>
-      </c>
-      <c r="AE2345">
-        <v>0</v>
-      </c>
-      <c r="AF2345">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2346" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2346" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2346" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2346" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2346" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2346">
-        <v>0</v>
-      </c>
-      <c r="AC2346">
-        <v>0</v>
-      </c>
-      <c r="AD2346">
-        <v>0</v>
-      </c>
-      <c r="AE2346">
-        <v>0</v>
-      </c>
-      <c r="AF2346">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2347" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2347" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2347" t="s">
-        <v>484</v>
-      </c>
-      <c r="K2347" t="s">
-        <v>484</v>
-      </c>
-      <c r="AA2347" s="1">
-        <v>45894</v>
-      </c>
-      <c r="AB2347">
-        <v>0</v>
-      </c>
-      <c r="AC2347">
-        <v>0</v>
-      </c>
-      <c r="AD2347">
-        <v>0</v>
-      </c>
-      <c r="AE2347">
-        <v>0</v>
-      </c>
-      <c r="AF2347">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2348" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AA2336" s="1"/>
+    </row>
+    <row r="2337" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2337" s="1"/>
+    </row>
+    <row r="2338" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2338" s="1"/>
+    </row>
+    <row r="2339" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2339" s="1"/>
+    </row>
+    <row r="2340" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2340" s="1"/>
+    </row>
+    <row r="2341" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2341" s="1"/>
+    </row>
+    <row r="2342" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2342" s="1"/>
+    </row>
+    <row r="2343" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2343" s="1"/>
+    </row>
+    <row r="2344" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2344" s="1"/>
+    </row>
+    <row r="2345" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2345" s="1"/>
+    </row>
+    <row r="2346" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2346" s="1"/>
+    </row>
+    <row r="2347" spans="27:32" x14ac:dyDescent="0.25">
+      <c r="AA2347" s="1"/>
+    </row>
+    <row r="2348" spans="27:32" x14ac:dyDescent="0.25">
       <c r="AA2348" s="1">
         <v>45894</v>
       </c>
@@ -61899,7 +60857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2349" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2349" spans="27:32" x14ac:dyDescent="0.25">
       <c r="AA2349" s="1">
         <v>45894</v>
       </c>
@@ -61919,7 +60877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2350" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2350" spans="27:32" x14ac:dyDescent="0.25">
       <c r="AA2350" s="1">
         <v>45894</v>
       </c>
@@ -61939,7 +60897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2351" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2351" spans="27:32" x14ac:dyDescent="0.25">
       <c r="AA2351" s="1">
         <v>45894</v>
       </c>
@@ -61959,7 +60917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2352" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2352" spans="27:32" x14ac:dyDescent="0.25">
       <c r="AA2352" s="1">
         <v>45894</v>
       </c>
@@ -63673,7 +62631,7 @@
         <v>21</v>
       </c>
       <c r="K2437" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L2437" t="s">
         <v>23</v>
@@ -63697,7 +62655,7 @@
         <v>29</v>
       </c>
       <c r="S2437" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T2437" t="s">
         <v>31</v>
@@ -65758,7 +64716,7 @@
         <v>5</v>
       </c>
       <c r="F2540" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="I2540" t="s">
         <v>7</v>
@@ -65819,7 +64777,7 @@
         <v>21</v>
       </c>
       <c r="K2542" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L2542" t="s">
         <v>23</v>
@@ -65843,7 +64801,7 @@
         <v>29</v>
       </c>
       <c r="S2542" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T2542" t="s">
         <v>31</v>
@@ -67904,7 +66862,7 @@
         <v>5</v>
       </c>
       <c r="F2645" t="s">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="I2645" t="s">
         <v>7</v>
@@ -67918,10 +66876,10 @@
     </row>
     <row r="2646" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C2646" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="F2646" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="I2646" t="s">
         <v>11</v>
@@ -68031,6 +66989,14 @@
         <v>43</v>
       </c>
     </row>
+    <row r="2648" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="D2648" t="s">
+        <v>467</v>
+      </c>
+      <c r="AA2648" s="1">
+        <v>45292</v>
+      </c>
+    </row>
     <row r="2649" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AB2649">
         <v>0</v>
@@ -70940,7 +69906,7 @@
         <v>5</v>
       </c>
       <c r="F2820" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="I2820" t="s">
         <v>7</v>
@@ -71001,7 +69967,7 @@
         <v>21</v>
       </c>
       <c r="K2822" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L2822" t="s">
         <v>23</v>
@@ -71025,7 +69991,7 @@
         <v>29</v>
       </c>
       <c r="S2822" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T2822" t="s">
         <v>31</v>
@@ -72786,7 +71752,7 @@
         <v>5</v>
       </c>
       <c r="F2925" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="I2925" t="s">
         <v>7</v>
@@ -72847,7 +71813,7 @@
         <v>21</v>
       </c>
       <c r="K2927" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L2927" t="s">
         <v>23</v>
@@ -72871,7 +71837,7 @@
         <v>29</v>
       </c>
       <c r="S2927" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T2927" t="s">
         <v>31</v>
@@ -72911,6 +71877,12 @@
       </c>
       <c r="AF2927" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="2928" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AA2928" s="1">
+        <f ca="1">TODAY()</f>
+        <v>45896</v>
       </c>
     </row>
     <row r="2929" spans="28:32" x14ac:dyDescent="0.25">
@@ -74632,7 +73604,7 @@
         <v>5</v>
       </c>
       <c r="F3030" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="I3030" t="s">
         <v>7</v>
@@ -74693,7 +73665,7 @@
         <v>21</v>
       </c>
       <c r="K3032" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L3032" t="s">
         <v>23</v>
@@ -74717,7 +73689,7 @@
         <v>29</v>
       </c>
       <c r="S3032" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T3032" t="s">
         <v>31</v>
@@ -74757,6 +73729,15 @@
       </c>
       <c r="AF3032" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="3033" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="D3033" t="s">
+        <v>468</v>
+      </c>
+      <c r="AA3033" s="1">
+        <f ca="1">TODAY()</f>
+        <v>45896</v>
       </c>
     </row>
     <row r="3034" spans="1:32" x14ac:dyDescent="0.25">
@@ -76478,7 +75459,7 @@
         <v>5</v>
       </c>
       <c r="F3135" t="s">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="I3135" t="s">
         <v>7</v>
@@ -76563,7 +75544,7 @@
         <v>29</v>
       </c>
       <c r="S3137" t="s">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="T3137" t="s">
         <v>31</v>
@@ -78321,7 +77302,7 @@
     </row>
     <row r="3252" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H3252" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/Test/OrthoMill1.xlsx
+++ b/Test/OrthoMill1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTWhitney\PycharmProjects\ScheduleDateRefresher\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23A4503-6954-4F68-A75C-CD225F653963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D71EE23-084C-4585-8FBE-326C9B0111C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="206" xr2:uid="{7D91035E-7C02-4707-AA65-6CEC655CC548}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3894" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3895" uniqueCount="470">
   <si>
     <t xml:space="preserve"> MILLING 1 SCHEDULE</t>
   </si>
@@ -1447,6 +1447,9 @@
   <si>
     <t>123456798-099</t>
   </si>
+  <si>
+    <t>04.315.301</t>
+  </si>
 </sst>
 </file>
 
@@ -2246,8 +2249,8 @@
       <c r="C11" t="s">
         <v>44</v>
       </c>
-      <c r="D11">
-        <v>42527451010</v>
+      <c r="D11" t="s">
+        <v>469</v>
       </c>
       <c r="E11">
         <v>50418000</v>
